--- a/outputs/32093.xlsx
+++ b/outputs/32093.xlsx
@@ -475,7 +475,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="str">
-        <f aca="false">IF(COUNTA(C2:E2)&gt;1,NA(),IF(C2&lt;&gt;"",C2,IF(D2&lt;&gt;"",D2,IF(E2&lt;&gt;"",E2,B2))))</f>
+        <f aca="false">IF(OR(C2&lt;&gt;"",D2&lt;&gt;"",E2&lt;&gt;""),IF(C2="",IF(D2="",E2,D2),C2),B2)</f>
         <v>Jim</v>
       </c>
       <c r="G2" s="1" t="str">
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="1" t="str">
-        <f aca="false">IF(COUNTA(C3:E3)&gt;1,NA(),IF(C3&lt;&gt;"",C3,IF(D3&lt;&gt;"",D3,IF(E3&lt;&gt;"",E3,B3))))</f>
+        <f aca="false">IF(OR(C3&lt;&gt;"",D3&lt;&gt;"",E3&lt;&gt;""),IF(C3="",IF(D3="",E3,D3),C3),B3)</f>
         <v>David</v>
       </c>
       <c r="G3" s="1" t="str">
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="str">
-        <f aca="false">IF(COUNTA(C4:E4)&gt;1,NA(),IF(C4&lt;&gt;"",C4,IF(D4&lt;&gt;"",D4,IF(E4&lt;&gt;"",E4,B4))))</f>
+        <f aca="false">IF(OR(C4&lt;&gt;"",D4&lt;&gt;"",E4&lt;&gt;""),IF(C4="",IF(D4="",E4,D4),C4),B4)</f>
         <v>David</v>
       </c>
       <c r="G4" s="1" t="str">
@@ -538,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="str">
-        <f aca="false">IF(COUNTA(C5:E5)&gt;1,NA(),IF(C5&lt;&gt;"",C5,IF(D5&lt;&gt;"",D5,IF(E5&lt;&gt;"",E5,B5))))</f>
+        <f aca="false">IF(OR(C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;""),IF(C5="",IF(D5="",E5,D5),C5),B5)</f>
         <v>Connor</v>
       </c>
       <c r="G5" s="1" t="str">
@@ -562,9 +562,9 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1" t="e">
-        <f aca="false">IF(COUNTA(C6:E6)&gt;1,NA(),IF(C6&lt;&gt;"",C6,IF(D6&lt;&gt;"",D6,IF(E6&lt;&gt;"",E6,B6))))</f>
-        <v>#N/A</v>
+      <c r="F6" s="1" t="str">
+        <f aca="false">IF(OR(C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;""),IF(C6="",IF(D6="",E6,D6),C6),B6)</f>
+        <v>Jeremy</v>
       </c>
       <c r="G6" s="1" t="str">
         <f aca="false">IF(C6="",B6,C6)</f>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="str">
-        <f aca="false">IF(COUNTA(C7:E7)&gt;1,NA(),IF(C7&lt;&gt;"",C7,IF(D7&lt;&gt;"",D7,IF(E7&lt;&gt;"",E7,B7))))</f>
+        <f aca="false">IF(OR(C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;""),IF(C7="",IF(D7="",E7,D7),C7),B7)</f>
         <v>Connor</v>
       </c>
       <c r="G7" s="1" t="str">
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="str">
-        <f aca="false">IF(COUNTA(C8:E8)&gt;1,NA(),IF(C8&lt;&gt;"",C8,IF(D8&lt;&gt;"",D8,IF(E8&lt;&gt;"",E8,B8))))</f>
+        <f aca="false">IF(OR(C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;""),IF(C8="",IF(D8="",E8,D8),C8),B8)</f>
         <v>Connor</v>
       </c>
       <c r="G8" s="1" t="str">
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="str">
-        <f aca="false">IF(COUNTA(C9:E9)&gt;1,NA(),IF(C9&lt;&gt;"",C9,IF(D9&lt;&gt;"",D9,IF(E9&lt;&gt;"",E9,B9))))</f>
+        <f aca="false">IF(OR(C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;""),IF(C9="",IF(D9="",E9,D9),C9),B9)</f>
         <v>Connor</v>
       </c>
       <c r="G9" s="1" t="str">
@@ -642,7 +642,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="1" t="str">
-        <f aca="false">IF(COUNTA(C10:E10)&gt;1,NA(),IF(C10&lt;&gt;"",C10,IF(D10&lt;&gt;"",D10,IF(E10&lt;&gt;"",E10,B10))))</f>
+        <f aca="false">IF(OR(C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;""),IF(C10="",IF(D10="",E10,D10),C10),B10)</f>
         <v>Susan</v>
       </c>
       <c r="G10" s="1" t="str">
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="str">
-        <f aca="false">IF(COUNTA(C11:E11)&gt;1,NA(),IF(C11&lt;&gt;"",C11,IF(D11&lt;&gt;"",D11,IF(E11&lt;&gt;"",E11,B11))))</f>
+        <f aca="false">IF(OR(C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;""),IF(C11="",IF(D11="",E11,D11),C11),B11)</f>
         <v>Gayle</v>
       </c>
       <c r="G11" s="1" t="str">
@@ -680,7 +680,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="1" t="str">
-        <f aca="false">IF(COUNTA(C12:E12)&gt;1,NA(),IF(C12&lt;&gt;"",C12,IF(D12&lt;&gt;"",D12,IF(E12&lt;&gt;"",E12,B12))))</f>
+        <f aca="false">IF(OR(C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;""),IF(C12="",IF(D12="",E12,D12),C12),B12)</f>
         <v>Gayle</v>
       </c>
       <c r="G12" s="1" t="str">
@@ -699,7 +699,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="1" t="str">
-        <f aca="false">IF(COUNTA(C13:E13)&gt;1,NA(),IF(C13&lt;&gt;"",C13,IF(D13&lt;&gt;"",D13,IF(E13&lt;&gt;"",E13,B13))))</f>
+        <f aca="false">IF(OR(C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;""),IF(C13="",IF(D13="",E13,D13),C13),B13)</f>
         <v>Gayle</v>
       </c>
       <c r="G13" s="1" t="str">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="1" t="str">
-        <f aca="false">IF(COUNTA(C14:E14)&gt;1,NA(),IF(C14&lt;&gt;"",C14,IF(D14&lt;&gt;"",D14,IF(E14&lt;&gt;"",E14,B14))))</f>
+        <f aca="false">IF(OR(C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;""),IF(C14="",IF(D14="",E14,D14),C14),B14)</f>
         <v>Gayle</v>
       </c>
       <c r="G14" s="1" t="str">
@@ -740,7 +740,7 @@
         <v>17</v>
       </c>
       <c r="F15" s="1" t="str">
-        <f aca="false">IF(COUNTA(C15:E15)&gt;1,NA(),IF(C15&lt;&gt;"",C15,IF(D15&lt;&gt;"",D15,IF(E15&lt;&gt;"",E15,B15))))</f>
+        <f aca="false">IF(OR(C15&lt;&gt;"",D15&lt;&gt;"",E15&lt;&gt;""),IF(C15="",IF(D15="",E15,D15),C15),B15)</f>
         <v>Douglas</v>
       </c>
       <c r="G15" s="1" t="str">
